--- a/District 227 - Mastersheet.xlsx
+++ b/District 227 - Mastersheet.xlsx
@@ -6475,16 +6475,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L4" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N4" s="17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O4" s="17" t="n">
         <v>0</v>
@@ -6664,16 +6664,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L7" s="20" t="n">
         <v>10</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N7" s="20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O7" s="20" t="n">
         <v>0</v>
@@ -6856,10 +6856,10 @@
         <v>5</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10" s="17" t="n">
         <v>5</v>
@@ -6868,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="17" t="n">
         <v>0</v>
@@ -7042,22 +7042,22 @@
         <v>0</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L13" s="20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="N13" s="20" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O13" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q13" s="20" t="n">
         <v>0</v>
@@ -7105,16 +7105,16 @@
         <v>1</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N14" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" s="17" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>2</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N15" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="20" t="n">
         <v>0</v>
@@ -7231,22 +7231,22 @@
         <v>0</v>
       </c>
       <c r="K16" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="L16" s="17" t="n">
-        <v>2</v>
-      </c>
       <c r="M16" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N16" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17" t="n">
         <v>3</v>
-      </c>
-      <c r="O16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="17" t="n">
-        <v>2</v>
       </c>
       <c r="Q16" s="17" t="n">
         <v>0</v>
@@ -7294,16 +7294,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N17" s="20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="20" t="n">
         <v>0</v>
@@ -7357,16 +7357,16 @@
         <v>0</v>
       </c>
       <c r="K18" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O18" s="17" t="n">
         <v>0</v>
@@ -7474,31 +7474,31 @@
         <v>8</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K20" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L20" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="N20" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="17" t="n">
         <v>0</v>
@@ -7672,16 +7672,16 @@
         <v>0</v>
       </c>
       <c r="K23" s="20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L23" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N23" s="20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O23" s="20" t="n">
         <v>0</v>
@@ -7987,22 +7987,22 @@
         <v>2</v>
       </c>
       <c r="K28" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L28" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M28" s="17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N28" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O28" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q28" s="17" t="n">
         <v>0</v>
@@ -8176,22 +8176,22 @@
         <v>0</v>
       </c>
       <c r="K31" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N31" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O31" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="20" t="n">
         <v>0</v>
@@ -8428,22 +8428,22 @@
         <v>5</v>
       </c>
       <c r="K35" s="20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="L35" s="20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M35" s="20" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="N35" s="20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="O35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q35" s="20" t="n">
         <v>0</v>
@@ -8491,22 +8491,22 @@
         <v>1</v>
       </c>
       <c r="K36" s="17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L36" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M36" s="17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N36" s="17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O36" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q36" s="17" t="n">
         <v>0</v>
@@ -8617,22 +8617,22 @@
         <v>0</v>
       </c>
       <c r="K38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="17" t="n">
-        <v>6</v>
-      </c>
       <c r="M38" s="17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="17" t="n">
         <v>7</v>
-      </c>
-      <c r="O38" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" s="17" t="n">
-        <v>6</v>
       </c>
       <c r="Q38" s="17" t="n">
         <v>0</v>
@@ -8995,22 +8995,22 @@
         <v>0</v>
       </c>
       <c r="K44" s="17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L44" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M44" s="17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N44" s="17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O44" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q44" s="17" t="n">
         <v>0</v>
@@ -9184,22 +9184,22 @@
         <v>0</v>
       </c>
       <c r="K47" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="L47" s="20" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="20" t="n">
         <v>1</v>
-      </c>
-      <c r="N47" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="Q47" s="20" t="n">
         <v>0</v>
@@ -9436,22 +9436,22 @@
         <v>2</v>
       </c>
       <c r="K51" s="20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L51" s="20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N51" s="20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O51" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q51" s="20" t="n">
         <v>0</v>
@@ -9877,22 +9877,22 @@
         <v>2</v>
       </c>
       <c r="K58" s="17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L58" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M58" s="17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N58" s="17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O58" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q58" s="17" t="n">
         <v>0</v>
@@ -10120,31 +10120,31 @@
         <v>33</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I62" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="17" t="n">
-        <v>0</v>
-      </c>
       <c r="K62" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L62" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N62" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q62" s="17" t="n">
         <v>0</v>
@@ -10375,28 +10375,28 @@
         <v>61</v>
       </c>
       <c r="I66" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="17" t="n">
         <v>2</v>
       </c>
       <c r="K66" s="17" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="L66" s="17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="M66" s="17" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="N66" s="17" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="O66" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="Q66" s="17" t="n">
         <v>0</v>
@@ -10696,22 +10696,22 @@
         <v>2</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L71" s="20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M71" s="20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="N71" s="20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O71" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q71" s="20" t="n">
         <v>0</v>
@@ -11011,22 +11011,22 @@
         <v>6</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L76" s="17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M76" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="N76" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="N76" s="17" t="n">
-        <v>7</v>
-      </c>
       <c r="O76" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q76" s="17" t="n">
         <v>0</v>
@@ -11452,16 +11452,16 @@
         <v>0</v>
       </c>
       <c r="K83" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" s="20" t="n">
         <v>0</v>
@@ -11515,22 +11515,22 @@
         <v>1</v>
       </c>
       <c r="K84" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L84" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="L84" s="17" t="n">
-        <v>0</v>
-      </c>
       <c r="M84" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N84" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="17" t="n">
         <v>1</v>
-      </c>
-      <c r="O84" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="17" t="n">
-        <v>0</v>
       </c>
       <c r="Q84" s="17" t="n">
         <v>0</v>
@@ -11641,16 +11641,16 @@
         <v>0</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L86" s="17" t="n">
         <v>3</v>
       </c>
       <c r="M86" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N86" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -11767,22 +11767,22 @@
         <v>2</v>
       </c>
       <c r="K88" s="17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L88" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M88" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="N88" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="O88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" s="17" t="n">
         <v>6</v>
-      </c>
-      <c r="N88" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O88" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" s="17" t="n">
-        <v>1</v>
       </c>
       <c r="Q88" s="17" t="n">
         <v>0</v>
@@ -11830,22 +11830,22 @@
         <v>1</v>
       </c>
       <c r="K89" s="20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L89" s="20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M89" s="20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N89" s="20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O89" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q89" s="20" t="n">
         <v>0</v>
@@ -12208,22 +12208,22 @@
         <v>1</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L95" s="20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M95" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="N95" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="O95" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="20" t="n">
         <v>3</v>
-      </c>
-      <c r="N95" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O95" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="20" t="n">
-        <v>1</v>
       </c>
       <c r="Q95" s="20" t="n">
         <v>0</v>
@@ -12460,16 +12460,16 @@
         <v>0</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L99" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O99" s="20" t="n">
         <v>0</v>
@@ -12523,22 +12523,22 @@
         <v>0</v>
       </c>
       <c r="K100" s="17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L100" s="17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M100" s="17" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="N100" s="17" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q100" s="17" t="n">
         <v>0</v>
@@ -12649,22 +12649,22 @@
         <v>0</v>
       </c>
       <c r="K102" s="17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L102" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M102" s="17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N102" s="17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O102" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q102" s="17" t="n">
         <v>0</v>
@@ -12712,22 +12712,22 @@
         <v>0</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L103" s="20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M103" s="20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N103" s="20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O103" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q103" s="20" t="n">
         <v>0</v>
@@ -12901,16 +12901,16 @@
         <v>1</v>
       </c>
       <c r="K106" s="17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L106" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N106" s="17" t="n">
         <v>17</v>
-      </c>
-      <c r="N106" s="17" t="n">
-        <v>16</v>
       </c>
       <c r="O106" s="17" t="n">
         <v>0</v>
@@ -13027,22 +13027,22 @@
         <v>3</v>
       </c>
       <c r="K108" s="17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L108" s="17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M108" s="17" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N108" s="17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O108" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q108" s="17" t="n">
         <v>0</v>
@@ -13279,22 +13279,22 @@
         <v>0</v>
       </c>
       <c r="K112" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="L112" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="L112" s="17" t="n">
-        <v>10</v>
-      </c>
       <c r="M112" s="17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N112" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="O112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="17" t="n">
         <v>11</v>
-      </c>
-      <c r="O112" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" s="17" t="n">
-        <v>10</v>
       </c>
       <c r="Q112" s="17" t="n">
         <v>0</v>
@@ -13459,31 +13459,31 @@
         <v>30</v>
       </c>
       <c r="H115" s="20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I115" s="20" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L115" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M115" s="20" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="N115" s="20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O115" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q115" s="20" t="n">
         <v>0</v>
@@ -14098,22 +14098,22 @@
         <v>0</v>
       </c>
       <c r="K125" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L125" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="L125" s="20" t="n">
-        <v>2</v>
-      </c>
       <c r="M125" s="20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N125" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="O125" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="20" t="n">
         <v>3</v>
-      </c>
-      <c r="O125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" s="20" t="n">
-        <v>2</v>
       </c>
       <c r="Q125" s="20" t="n">
         <v>0</v>
@@ -14161,22 +14161,22 @@
         <v>0</v>
       </c>
       <c r="K126" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L126" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N126" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q126" s="17" t="n">
         <v>0</v>
@@ -14287,22 +14287,22 @@
         <v>1</v>
       </c>
       <c r="K128" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L128" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="L128" s="17" t="n">
-        <v>3</v>
-      </c>
       <c r="M128" s="17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N128" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="O128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="17" t="n">
         <v>4</v>
-      </c>
-      <c r="O128" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="17" t="n">
-        <v>3</v>
       </c>
       <c r="Q128" s="17" t="n">
         <v>0</v>
@@ -14476,16 +14476,16 @@
         <v>0</v>
       </c>
       <c r="K131" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M131" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N131" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" s="20" t="n">
         <v>0</v>
@@ -14539,22 +14539,22 @@
         <v>0</v>
       </c>
       <c r="K132" s="17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L132" s="17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M132" s="17" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N132" s="17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O132" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q132" s="17" t="n">
         <v>0</v>
@@ -14917,22 +14917,22 @@
         <v>3</v>
       </c>
       <c r="K138" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L138" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M138" s="17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N138" s="17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O138" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q138" s="17" t="n">
         <v>0</v>
@@ -14980,16 +14980,16 @@
         <v>0</v>
       </c>
       <c r="K139" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L139" s="20" t="n">
         <v>2</v>
       </c>
       <c r="M139" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N139" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O139" s="20" t="n">
         <v>0</v>
@@ -15169,22 +15169,22 @@
         <v>7</v>
       </c>
       <c r="K142" s="17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L142" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M142" s="17" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="N142" s="17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="O142" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P142" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q142" s="17" t="n">
         <v>0</v>
@@ -15484,16 +15484,16 @@
         <v>0</v>
       </c>
       <c r="K147" s="20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L147" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N147" s="20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O147" s="20" t="n">
         <v>0</v>
@@ -15673,16 +15673,16 @@
         <v>0</v>
       </c>
       <c r="K150" s="17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L150" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M150" s="17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N150" s="17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O150" s="17" t="n">
         <v>0</v>

--- a/District 227 - Mastersheet.xlsx
+++ b/District 227 - Mastersheet.xlsx
@@ -6538,22 +6538,22 @@
         <v>0</v>
       </c>
       <c r="K5" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" s="20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M5" s="20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N5" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="20" t="n">
         <v>0</v>
@@ -6664,22 +6664,22 @@
         <v>0</v>
       </c>
       <c r="K7" s="20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N7" s="20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O7" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q7" s="20" t="n">
         <v>0</v>
@@ -6844,25 +6844,25 @@
         <v>27</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I10" s="17" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L10" s="17" t="n">
         <v>3</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N10" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O10" s="17" t="n">
         <v>0</v>
@@ -7042,22 +7042,22 @@
         <v>0</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L13" s="20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="N13" s="20" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O13" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q13" s="20" t="n">
         <v>0</v>
@@ -7105,16 +7105,16 @@
         <v>1</v>
       </c>
       <c r="K14" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" s="17" t="n">
         <v>4</v>
-      </c>
-      <c r="N14" s="17" t="n">
-        <v>3</v>
       </c>
       <c r="O14" s="17" t="n">
         <v>0</v>
@@ -7168,16 +7168,16 @@
         <v>2</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L15" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" s="20" t="n">
         <v>7</v>
-      </c>
-      <c r="N15" s="20" t="n">
-        <v>5</v>
       </c>
       <c r="O15" s="20" t="n">
         <v>0</v>
@@ -7231,22 +7231,22 @@
         <v>0</v>
       </c>
       <c r="K16" s="17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L16" s="17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M16" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17" t="n">
         <v>7</v>
-      </c>
-      <c r="N16" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="17" t="n">
-        <v>3</v>
       </c>
       <c r="Q16" s="17" t="n">
         <v>0</v>
@@ -7294,16 +7294,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17" s="20" t="n">
         <v>0</v>
@@ -7357,16 +7357,16 @@
         <v>0</v>
       </c>
       <c r="K18" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N18" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O18" s="17" t="n">
         <v>0</v>
@@ -7609,22 +7609,22 @@
         <v>0</v>
       </c>
       <c r="K22" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="L22" s="17" t="n">
-        <v>4</v>
-      </c>
       <c r="M22" s="17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N22" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="17" t="n">
         <v>5</v>
-      </c>
-      <c r="O22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="17" t="n">
-        <v>4</v>
       </c>
       <c r="Q22" s="17" t="n">
         <v>0</v>
@@ -7924,22 +7924,22 @@
         <v>0</v>
       </c>
       <c r="K27" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="20" t="n">
         <v>0</v>
@@ -7987,16 +7987,16 @@
         <v>2</v>
       </c>
       <c r="K28" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L28" s="17" t="n">
         <v>9</v>
       </c>
       <c r="M28" s="17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N28" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O28" s="17" t="n">
         <v>0</v>
@@ -8176,16 +8176,16 @@
         <v>0</v>
       </c>
       <c r="K31" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="20" t="n">
         <v>3</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N31" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O31" s="20" t="n">
         <v>0</v>
@@ -8428,22 +8428,22 @@
         <v>5</v>
       </c>
       <c r="K35" s="20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L35" s="20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M35" s="20" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="N35" s="20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O35" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q35" s="20" t="n">
         <v>0</v>
@@ -8617,22 +8617,22 @@
         <v>0</v>
       </c>
       <c r="K38" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L38" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M38" s="17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="N38" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O38" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q38" s="17" t="n">
         <v>0</v>
@@ -8995,22 +8995,22 @@
         <v>0</v>
       </c>
       <c r="K44" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L44" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M44" s="17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N44" s="17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O44" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q44" s="17" t="n">
         <v>0</v>
@@ -9184,16 +9184,16 @@
         <v>0</v>
       </c>
       <c r="K47" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" s="20" t="n">
         <v>1</v>
       </c>
       <c r="M47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" s="20" t="n">
         <v>3</v>
-      </c>
-      <c r="N47" s="20" t="n">
-        <v>2</v>
       </c>
       <c r="O47" s="20" t="n">
         <v>0</v>
@@ -9436,22 +9436,22 @@
         <v>2</v>
       </c>
       <c r="K51" s="20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L51" s="20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N51" s="20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O51" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q51" s="20" t="n">
         <v>0</v>
@@ -10003,16 +10003,16 @@
         <v>0</v>
       </c>
       <c r="K60" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N60" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" s="17" t="n">
         <v>0</v>
@@ -10129,22 +10129,22 @@
         <v>1</v>
       </c>
       <c r="K62" s="17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L62" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N62" s="17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q62" s="17" t="n">
         <v>0</v>
@@ -10381,22 +10381,22 @@
         <v>2</v>
       </c>
       <c r="K66" s="17" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L66" s="17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M66" s="17" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="N66" s="17" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="O66" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q66" s="17" t="n">
         <v>0</v>
@@ -10696,16 +10696,16 @@
         <v>2</v>
       </c>
       <c r="K71" s="20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L71" s="20" t="n">
         <v>11</v>
       </c>
       <c r="M71" s="20" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N71" s="20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O71" s="20" t="n">
         <v>0</v>
@@ -10822,16 +10822,16 @@
         <v>0</v>
       </c>
       <c r="K73" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73" s="20" t="n">
         <v>1</v>
       </c>
       <c r="M73" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N73" s="20" t="n">
         <v>4</v>
-      </c>
-      <c r="N73" s="20" t="n">
-        <v>3</v>
       </c>
       <c r="O73" s="20" t="n">
         <v>0</v>
@@ -11011,16 +11011,16 @@
         <v>6</v>
       </c>
       <c r="K76" s="17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L76" s="17" t="n">
         <v>13</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N76" s="17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O76" s="17" t="n">
         <v>0</v>
@@ -11263,16 +11263,16 @@
         <v>0</v>
       </c>
       <c r="K80" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L80" s="17" t="n">
         <v>2</v>
       </c>
       <c r="M80" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N80" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O80" s="17" t="n">
         <v>0</v>
@@ -11515,22 +11515,22 @@
         <v>1</v>
       </c>
       <c r="K84" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L84" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N84" s="17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O84" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="17" t="n">
         <v>0</v>
@@ -11641,16 +11641,16 @@
         <v>0</v>
       </c>
       <c r="K86" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L86" s="17" t="n">
         <v>3</v>
       </c>
       <c r="M86" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N86" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -12208,22 +12208,22 @@
         <v>1</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L95" s="20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M95" s="20" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="N95" s="20" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="O95" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q95" s="20" t="n">
         <v>0</v>
@@ -12460,22 +12460,22 @@
         <v>0</v>
       </c>
       <c r="K99" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="L99" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="L99" s="20" t="n">
-        <v>0</v>
-      </c>
       <c r="M99" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N99" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="20" t="n">
         <v>2</v>
-      </c>
-      <c r="N99" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="20" t="n">
-        <v>0</v>
       </c>
       <c r="Q99" s="20" t="n">
         <v>0</v>
@@ -12523,16 +12523,16 @@
         <v>0</v>
       </c>
       <c r="K100" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L100" s="17" t="n">
         <v>8</v>
       </c>
       <c r="M100" s="17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N100" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O100" s="17" t="n">
         <v>0</v>
@@ -12649,22 +12649,22 @@
         <v>0</v>
       </c>
       <c r="K102" s="17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L102" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M102" s="17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N102" s="17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O102" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q102" s="17" t="n">
         <v>0</v>
@@ -12712,16 +12712,16 @@
         <v>0</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L103" s="20" t="n">
         <v>10</v>
       </c>
       <c r="M103" s="20" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N103" s="20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O103" s="20" t="n">
         <v>0</v>
@@ -12895,22 +12895,22 @@
         <v>42</v>
       </c>
       <c r="I106" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J106" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="17" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L106" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M106" s="17" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N106" s="17" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="O106" s="17" t="n">
         <v>0</v>
@@ -13027,22 +13027,22 @@
         <v>3</v>
       </c>
       <c r="K108" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L108" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M108" s="17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N108" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O108" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q108" s="17" t="n">
         <v>0</v>
@@ -13090,16 +13090,16 @@
         <v>2</v>
       </c>
       <c r="K109" s="20" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L109" s="20" t="n">
         <v>1</v>
       </c>
       <c r="M109" s="20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="N109" s="20" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="O109" s="20" t="n">
         <v>0</v>
@@ -13279,16 +13279,16 @@
         <v>0</v>
       </c>
       <c r="K112" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L112" s="17" t="n">
         <v>11</v>
       </c>
       <c r="M112" s="17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N112" s="17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O112" s="17" t="n">
         <v>0</v>
@@ -13342,16 +13342,16 @@
         <v>0</v>
       </c>
       <c r="K113" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M113" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N113" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" s="20" t="n">
         <v>0</v>
@@ -13459,31 +13459,31 @@
         <v>30</v>
       </c>
       <c r="H115" s="20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I115" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K115" s="20" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L115" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M115" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="N115" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="N115" s="20" t="n">
-        <v>12</v>
-      </c>
       <c r="O115" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q115" s="20" t="n">
         <v>0</v>
@@ -13720,22 +13720,22 @@
         <v>1</v>
       </c>
       <c r="K119" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L119" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M119" s="20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N119" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O119" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P119" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q119" s="20" t="n">
         <v>0</v>
@@ -13846,22 +13846,22 @@
         <v>0</v>
       </c>
       <c r="K121" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L121" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="N121" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="N121" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="O121" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="20" t="n">
         <v>0</v>
@@ -13909,16 +13909,16 @@
         <v>0</v>
       </c>
       <c r="K122" s="17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L122" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M122" s="17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N122" s="17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O122" s="17" t="n">
         <v>0</v>
@@ -13963,31 +13963,31 @@
         <v>15</v>
       </c>
       <c r="H123" s="20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I123" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J123" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K123" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L123" s="20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M123" s="20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N123" s="20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O123" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="20" t="n">
         <v>0</v>
@@ -14098,16 +14098,16 @@
         <v>0</v>
       </c>
       <c r="K125" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L125" s="20" t="n">
         <v>3</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N125" s="20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O125" s="20" t="n">
         <v>0</v>
@@ -14161,22 +14161,22 @@
         <v>0</v>
       </c>
       <c r="K126" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L126" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N126" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q126" s="17" t="n">
         <v>0</v>
@@ -14290,10 +14290,10 @@
         <v>6</v>
       </c>
       <c r="L128" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M128" s="17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N128" s="17" t="n">
         <v>6</v>
@@ -14302,7 +14302,7 @@
         <v>0</v>
       </c>
       <c r="P128" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q128" s="17" t="n">
         <v>0</v>
@@ -14476,22 +14476,22 @@
         <v>0</v>
       </c>
       <c r="K131" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L131" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N131" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O131" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q131" s="20" t="n">
         <v>0</v>
@@ -14917,22 +14917,22 @@
         <v>3</v>
       </c>
       <c r="K138" s="17" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L138" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M138" s="17" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="N138" s="17" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="O138" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q138" s="17" t="n">
         <v>0</v>
@@ -14980,22 +14980,22 @@
         <v>0</v>
       </c>
       <c r="K139" s="20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L139" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M139" s="20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N139" s="20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O139" s="20" t="n">
         <v>0</v>
       </c>
       <c r="P139" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q139" s="20" t="n">
         <v>0</v>
@@ -15169,16 +15169,16 @@
         <v>7</v>
       </c>
       <c r="K142" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L142" s="17" t="n">
         <v>13</v>
       </c>
       <c r="M142" s="17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N142" s="17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O142" s="17" t="n">
         <v>0</v>
@@ -15232,16 +15232,16 @@
         <v>9</v>
       </c>
       <c r="K143" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L143" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M143" s="20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N143" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O143" s="20" t="n">
         <v>0</v>
@@ -15358,16 +15358,16 @@
         <v>0</v>
       </c>
       <c r="K145" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L145" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M145" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N145" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O145" s="20" t="n">
         <v>0</v>
@@ -15484,16 +15484,16 @@
         <v>0</v>
       </c>
       <c r="K147" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L147" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N147" s="20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O147" s="20" t="n">
         <v>0</v>
@@ -15673,16 +15673,16 @@
         <v>0</v>
       </c>
       <c r="K150" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L150" s="17" t="n">
         <v>0</v>
       </c>
       <c r="M150" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N150" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O150" s="17" t="n">
         <v>0</v>
